--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D844"/>
+  <dimension ref="A1:D845"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15519,16 +15519,16 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/12</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C839" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D839" t="n">
         <v>101</v>
@@ -15537,12 +15537,12 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -15555,12 +15555,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -15573,12 +15573,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -15591,12 +15591,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -15609,18 +15609,36 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C844" t="n">
+        <v>22</v>
+      </c>
+      <c r="D844" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B844" t="inlineStr">
+      <c r="B845" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C844" t="n">
-        <v>22</v>
-      </c>
-      <c r="D844" t="n">
+      <c r="C845" t="n">
+        <v>22</v>
+      </c>
+      <c r="D845" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D845"/>
+  <dimension ref="A1:D846"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15537,16 +15537,16 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/13</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C840" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D840" t="n">
         <v>101</v>
@@ -15555,12 +15555,12 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -15573,12 +15573,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -15591,12 +15591,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -15609,12 +15609,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -15627,18 +15627,36 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C845" t="n">
+        <v>22</v>
+      </c>
+      <c r="D845" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B845" t="inlineStr">
+      <c r="B846" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C845" t="n">
-        <v>22</v>
-      </c>
-      <c r="D845" t="n">
+      <c r="C846" t="n">
+        <v>22</v>
+      </c>
+      <c r="D846" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D846"/>
+  <dimension ref="A1:D847"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15555,16 +15555,16 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/14</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C841" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D841" t="n">
         <v>101</v>
@@ -15573,12 +15573,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -15591,12 +15591,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -15609,12 +15609,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -15627,12 +15627,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -15645,18 +15645,36 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C846" t="n">
+        <v>22</v>
+      </c>
+      <c r="D846" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B846" t="inlineStr">
+      <c r="B847" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C846" t="n">
-        <v>22</v>
-      </c>
-      <c r="D846" t="n">
+      <c r="C847" t="n">
+        <v>22</v>
+      </c>
+      <c r="D847" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D847"/>
+  <dimension ref="A1:D848"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15573,7 +15573,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/15</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -15582,7 +15582,7 @@
         </is>
       </c>
       <c r="C842" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D842" t="n">
         <v>101</v>
@@ -15591,12 +15591,12 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -15609,12 +15609,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -15627,12 +15627,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -15645,12 +15645,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -15663,18 +15663,36 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C847" t="n">
+        <v>22</v>
+      </c>
+      <c r="D847" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B847" t="inlineStr">
+      <c r="B848" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C847" t="n">
-        <v>22</v>
-      </c>
-      <c r="D847" t="n">
+      <c r="C848" t="n">
+        <v>22</v>
+      </c>
+      <c r="D848" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D848"/>
+  <dimension ref="A1:D849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15591,16 +15591,16 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/16</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C843" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D843" t="n">
         <v>101</v>
@@ -15609,12 +15609,12 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -15627,12 +15627,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -15645,12 +15645,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -15663,12 +15663,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -15681,18 +15681,36 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C848" t="n">
+        <v>22</v>
+      </c>
+      <c r="D848" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B848" t="inlineStr">
+      <c r="B849" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C848" t="n">
-        <v>22</v>
-      </c>
-      <c r="D848" t="n">
+      <c r="C849" t="n">
+        <v>22</v>
+      </c>
+      <c r="D849" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D849"/>
+  <dimension ref="A1:D850"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15609,16 +15609,16 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/17</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C844" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D844" t="n">
         <v>101</v>
@@ -15627,12 +15627,12 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -15645,12 +15645,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -15663,12 +15663,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -15681,12 +15681,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -15699,18 +15699,36 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C849" t="n">
+        <v>22</v>
+      </c>
+      <c r="D849" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B849" t="inlineStr">
+      <c r="B850" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C849" t="n">
-        <v>22</v>
-      </c>
-      <c r="D849" t="n">
+      <c r="C850" t="n">
+        <v>22</v>
+      </c>
+      <c r="D850" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D850"/>
+  <dimension ref="A1:D851"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15627,16 +15627,16 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/18</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C845" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D845" t="n">
         <v>101</v>
@@ -15645,12 +15645,12 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -15663,12 +15663,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -15681,12 +15681,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -15699,12 +15699,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -15717,18 +15717,36 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C850" t="n">
+        <v>22</v>
+      </c>
+      <c r="D850" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B850" t="inlineStr">
+      <c r="B851" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C850" t="n">
-        <v>22</v>
-      </c>
-      <c r="D850" t="n">
+      <c r="C851" t="n">
+        <v>22</v>
+      </c>
+      <c r="D851" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D851"/>
+  <dimension ref="A1:D852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15645,16 +15645,16 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/19</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C846" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D846" t="n">
         <v>101</v>
@@ -15663,12 +15663,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -15681,12 +15681,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -15699,12 +15699,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -15717,12 +15717,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -15735,18 +15735,36 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C851" t="n">
+        <v>22</v>
+      </c>
+      <c r="D851" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B851" t="inlineStr">
+      <c r="B852" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C851" t="n">
-        <v>22</v>
-      </c>
-      <c r="D851" t="n">
+      <c r="C852" t="n">
+        <v>22</v>
+      </c>
+      <c r="D852" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D852"/>
+  <dimension ref="A1:D853"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15663,16 +15663,16 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/20</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C847" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D847" t="n">
         <v>101</v>
@@ -15681,12 +15681,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -15699,12 +15699,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -15717,12 +15717,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -15735,12 +15735,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -15753,18 +15753,36 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C852" t="n">
+        <v>22</v>
+      </c>
+      <c r="D852" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B852" t="inlineStr">
+      <c r="B853" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C852" t="n">
-        <v>22</v>
-      </c>
-      <c r="D852" t="n">
+      <c r="C853" t="n">
+        <v>22</v>
+      </c>
+      <c r="D853" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D853"/>
+  <dimension ref="A1:D854"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15681,16 +15681,16 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/21</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C848" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D848" t="n">
         <v>101</v>
@@ -15699,12 +15699,12 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -15717,12 +15717,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -15735,12 +15735,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -15753,12 +15753,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -15771,18 +15771,36 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C853" t="n">
+        <v>22</v>
+      </c>
+      <c r="D853" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B853" t="inlineStr">
+      <c r="B854" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C853" t="n">
-        <v>22</v>
-      </c>
-      <c r="D853" t="n">
+      <c r="C854" t="n">
+        <v>22</v>
+      </c>
+      <c r="D854" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D854"/>
+  <dimension ref="A1:D855"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15699,7 +15699,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/22</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -15708,7 +15708,7 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D849" t="n">
         <v>101</v>
@@ -15717,12 +15717,12 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -15735,12 +15735,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -15753,12 +15753,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -15771,12 +15771,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -15789,18 +15789,36 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C854" t="n">
+        <v>22</v>
+      </c>
+      <c r="D854" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B854" t="inlineStr">
+      <c r="B855" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C854" t="n">
-        <v>22</v>
-      </c>
-      <c r="D854" t="n">
+      <c r="C855" t="n">
+        <v>22</v>
+      </c>
+      <c r="D855" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D855"/>
+  <dimension ref="A1:D856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15717,16 +15717,16 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/23</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C850" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D850" t="n">
         <v>101</v>
@@ -15735,12 +15735,12 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -15753,12 +15753,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -15771,12 +15771,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -15789,12 +15789,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -15807,18 +15807,36 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C855" t="n">
+        <v>22</v>
+      </c>
+      <c r="D855" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B855" t="inlineStr">
+      <c r="B856" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C855" t="n">
-        <v>22</v>
-      </c>
-      <c r="D855" t="n">
+      <c r="C856" t="n">
+        <v>22</v>
+      </c>
+      <c r="D856" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D856"/>
+  <dimension ref="A1:D857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15735,16 +15735,16 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/24</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C851" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D851" t="n">
         <v>101</v>
@@ -15753,12 +15753,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -15771,12 +15771,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -15789,12 +15789,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -15807,12 +15807,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -15825,18 +15825,36 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C856" t="n">
+        <v>22</v>
+      </c>
+      <c r="D856" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B856" t="inlineStr">
+      <c r="B857" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C856" t="n">
-        <v>22</v>
-      </c>
-      <c r="D856" t="n">
+      <c r="C857" t="n">
+        <v>22</v>
+      </c>
+      <c r="D857" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D857"/>
+  <dimension ref="A1:D858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15753,16 +15753,16 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/26</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C852" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D852" t="n">
         <v>101</v>
@@ -15771,12 +15771,12 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -15789,12 +15789,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -15807,12 +15807,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -15825,12 +15825,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -15843,18 +15843,36 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C857" t="n">
+        <v>22</v>
+      </c>
+      <c r="D857" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B857" t="inlineStr">
+      <c r="B858" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C857" t="n">
-        <v>22</v>
-      </c>
-      <c r="D857" t="n">
+      <c r="C858" t="n">
+        <v>22</v>
+      </c>
+      <c r="D858" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D858"/>
+  <dimension ref="A1:D859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15771,16 +15771,16 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/26</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C853" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D853" t="n">
         <v>101</v>
@@ -15789,12 +15789,12 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C854" t="n">
@@ -15807,12 +15807,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -15825,12 +15825,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -15843,12 +15843,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -15861,18 +15861,36 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C858" t="n">
+        <v>22</v>
+      </c>
+      <c r="D858" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B858" t="inlineStr">
+      <c r="B859" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C858" t="n">
-        <v>22</v>
-      </c>
-      <c r="D858" t="n">
+      <c r="C859" t="n">
+        <v>22</v>
+      </c>
+      <c r="D859" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D859"/>
+  <dimension ref="A1:D860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15789,16 +15789,16 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/27</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C854" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D854" t="n">
         <v>101</v>
@@ -15807,12 +15807,12 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -15825,12 +15825,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -15843,12 +15843,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -15861,12 +15861,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -15879,18 +15879,36 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C859" t="n">
+        <v>22</v>
+      </c>
+      <c r="D859" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B859" t="inlineStr">
+      <c r="B860" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C859" t="n">
-        <v>22</v>
-      </c>
-      <c r="D859" t="n">
+      <c r="C860" t="n">
+        <v>22</v>
+      </c>
+      <c r="D860" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D860"/>
+  <dimension ref="A1:D861"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15807,16 +15807,16 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/28</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C855" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D855" t="n">
         <v>101</v>
@@ -15825,12 +15825,12 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C856" t="n">
@@ -15843,12 +15843,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -15861,12 +15861,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -15879,12 +15879,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -15897,18 +15897,36 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C860" t="n">
+        <v>22</v>
+      </c>
+      <c r="D860" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B860" t="inlineStr">
+      <c r="B861" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C860" t="n">
-        <v>22</v>
-      </c>
-      <c r="D860" t="n">
+      <c r="C861" t="n">
+        <v>22</v>
+      </c>
+      <c r="D861" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D861"/>
+  <dimension ref="A1:D862"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15825,16 +15825,16 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/30</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C856" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D856" t="n">
         <v>101</v>
@@ -15843,12 +15843,12 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -15861,12 +15861,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -15879,12 +15879,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -15897,12 +15897,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -15915,18 +15915,36 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C861" t="n">
+        <v>22</v>
+      </c>
+      <c r="D861" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B861" t="inlineStr">
+      <c r="B862" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C861" t="n">
-        <v>22</v>
-      </c>
-      <c r="D861" t="n">
+      <c r="C862" t="n">
+        <v>22</v>
+      </c>
+      <c r="D862" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D862"/>
+  <dimension ref="A1:D863"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15843,16 +15843,16 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/09/30</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C857" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D857" t="n">
         <v>101</v>
@@ -15861,12 +15861,12 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -15879,12 +15879,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -15897,12 +15897,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -15915,12 +15915,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -15933,18 +15933,36 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C862" t="n">
+        <v>22</v>
+      </c>
+      <c r="D862" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B862" t="inlineStr">
+      <c r="B863" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C862" t="n">
-        <v>22</v>
-      </c>
-      <c r="D862" t="n">
+      <c r="C863" t="n">
+        <v>22</v>
+      </c>
+      <c r="D863" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D863"/>
+  <dimension ref="A1:D864"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15861,16 +15861,16 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/01</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C858" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D858" t="n">
         <v>101</v>
@@ -15879,12 +15879,12 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -15897,12 +15897,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -15915,12 +15915,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -15933,12 +15933,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -15951,18 +15951,36 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C863" t="n">
+        <v>22</v>
+      </c>
+      <c r="D863" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B863" t="inlineStr">
+      <c r="B864" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C863" t="n">
-        <v>22</v>
-      </c>
-      <c r="D863" t="n">
+      <c r="C864" t="n">
+        <v>22</v>
+      </c>
+      <c r="D864" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D864"/>
+  <dimension ref="A1:D865"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15879,16 +15879,16 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/02</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C859" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D859" t="n">
         <v>101</v>
@@ -15897,12 +15897,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -15915,12 +15915,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -15933,12 +15933,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -15951,12 +15951,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -15969,18 +15969,36 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C864" t="n">
+        <v>22</v>
+      </c>
+      <c r="D864" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B864" t="inlineStr">
+      <c r="B865" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C864" t="n">
-        <v>22</v>
-      </c>
-      <c r="D864" t="n">
+      <c r="C865" t="n">
+        <v>22</v>
+      </c>
+      <c r="D865" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D865"/>
+  <dimension ref="A1:D866"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15897,12 +15897,12 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/03</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C860" t="n">
@@ -15915,12 +15915,12 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -15933,12 +15933,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -15951,12 +15951,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -15969,12 +15969,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -15987,18 +15987,36 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C865" t="n">
+        <v>22</v>
+      </c>
+      <c r="D865" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B865" t="inlineStr">
+      <c r="B866" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C865" t="n">
-        <v>22</v>
-      </c>
-      <c r="D865" t="n">
+      <c r="C866" t="n">
+        <v>22</v>
+      </c>
+      <c r="D866" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D866"/>
+  <dimension ref="A1:D867"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15915,16 +15915,16 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/04</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C861" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D861" t="n">
         <v>101</v>
@@ -15933,12 +15933,12 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -15951,12 +15951,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -15969,12 +15969,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -15987,12 +15987,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -16005,18 +16005,36 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C866" t="n">
+        <v>22</v>
+      </c>
+      <c r="D866" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B866" t="inlineStr">
+      <c r="B867" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C866" t="n">
-        <v>22</v>
-      </c>
-      <c r="D866" t="n">
+      <c r="C867" t="n">
+        <v>22</v>
+      </c>
+      <c r="D867" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D867"/>
+  <dimension ref="A1:D868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15933,16 +15933,16 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/05</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C862" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D862" t="n">
         <v>101</v>
@@ -15951,12 +15951,12 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -15969,12 +15969,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -15987,12 +15987,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -16005,12 +16005,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -16023,18 +16023,36 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C867" t="n">
+        <v>22</v>
+      </c>
+      <c r="D867" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B867" t="inlineStr">
+      <c r="B868" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C867" t="n">
-        <v>22</v>
-      </c>
-      <c r="D867" t="n">
+      <c r="C868" t="n">
+        <v>22</v>
+      </c>
+      <c r="D868" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D868"/>
+  <dimension ref="A1:D869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15951,7 +15951,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/06</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -15960,7 +15960,7 @@
         </is>
       </c>
       <c r="C863" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D863" t="n">
         <v>101</v>
@@ -15969,12 +15969,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -15987,12 +15987,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -16005,12 +16005,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -16023,12 +16023,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -16041,18 +16041,36 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C868" t="n">
+        <v>22</v>
+      </c>
+      <c r="D868" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B868" t="inlineStr">
+      <c r="B869" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C868" t="n">
-        <v>22</v>
-      </c>
-      <c r="D868" t="n">
+      <c r="C869" t="n">
+        <v>22</v>
+      </c>
+      <c r="D869" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D869"/>
+  <dimension ref="A1:D870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15969,16 +15969,16 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/07</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C864" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D864" t="n">
         <v>101</v>
@@ -15987,12 +15987,12 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -16005,12 +16005,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -16023,12 +16023,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -16041,12 +16041,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -16059,18 +16059,36 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C869" t="n">
+        <v>22</v>
+      </c>
+      <c r="D869" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B869" t="inlineStr">
+      <c r="B870" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C869" t="n">
-        <v>22</v>
-      </c>
-      <c r="D869" t="n">
+      <c r="C870" t="n">
+        <v>22</v>
+      </c>
+      <c r="D870" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D870"/>
+  <dimension ref="A1:D871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15987,16 +15987,16 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/08</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C865" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D865" t="n">
         <v>101</v>
@@ -16005,12 +16005,12 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -16023,12 +16023,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -16041,12 +16041,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -16059,12 +16059,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -16077,18 +16077,36 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C870" t="n">
+        <v>22</v>
+      </c>
+      <c r="D870" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B870" t="inlineStr">
+      <c r="B871" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C870" t="n">
-        <v>22</v>
-      </c>
-      <c r="D870" t="n">
+      <c r="C871" t="n">
+        <v>22</v>
+      </c>
+      <c r="D871" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D871"/>
+  <dimension ref="A1:D872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16005,16 +16005,16 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/09</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C866" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D866" t="n">
         <v>101</v>
@@ -16023,12 +16023,12 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -16041,12 +16041,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -16059,12 +16059,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -16077,12 +16077,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -16095,18 +16095,36 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C871" t="n">
+        <v>22</v>
+      </c>
+      <c r="D871" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B871" t="inlineStr">
+      <c r="B872" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C871" t="n">
-        <v>22</v>
-      </c>
-      <c r="D871" t="n">
+      <c r="C872" t="n">
+        <v>22</v>
+      </c>
+      <c r="D872" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D872"/>
+  <dimension ref="A1:D873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16023,16 +16023,16 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/10</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C867" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D867" t="n">
         <v>101</v>
@@ -16041,12 +16041,12 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -16059,12 +16059,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -16077,12 +16077,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -16095,12 +16095,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -16113,18 +16113,36 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C872" t="n">
+        <v>22</v>
+      </c>
+      <c r="D872" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B872" t="inlineStr">
+      <c r="B873" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C872" t="n">
-        <v>22</v>
-      </c>
-      <c r="D872" t="n">
+      <c r="C873" t="n">
+        <v>22</v>
+      </c>
+      <c r="D873" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D873"/>
+  <dimension ref="A1:D874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16041,16 +16041,16 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/11</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C868" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D868" t="n">
         <v>101</v>
@@ -16059,12 +16059,12 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -16077,12 +16077,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -16095,12 +16095,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -16113,12 +16113,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -16131,18 +16131,36 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C873" t="n">
+        <v>22</v>
+      </c>
+      <c r="D873" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B873" t="inlineStr">
+      <c r="B874" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C873" t="n">
-        <v>22</v>
-      </c>
-      <c r="D873" t="n">
+      <c r="C874" t="n">
+        <v>22</v>
+      </c>
+      <c r="D874" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D874"/>
+  <dimension ref="A1:D875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16059,16 +16059,16 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/12</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C869" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D869" t="n">
         <v>101</v>
@@ -16077,12 +16077,12 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -16095,12 +16095,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -16113,12 +16113,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -16131,12 +16131,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -16149,18 +16149,36 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C874" t="n">
+        <v>22</v>
+      </c>
+      <c r="D874" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B874" t="inlineStr">
+      <c r="B875" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C874" t="n">
-        <v>22</v>
-      </c>
-      <c r="D874" t="n">
+      <c r="C875" t="n">
+        <v>22</v>
+      </c>
+      <c r="D875" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D875"/>
+  <dimension ref="A1:D876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16077,7 +16077,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/13</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -16086,7 +16086,7 @@
         </is>
       </c>
       <c r="C870" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D870" t="n">
         <v>101</v>
@@ -16095,12 +16095,12 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -16113,12 +16113,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -16131,12 +16131,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -16149,12 +16149,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -16167,18 +16167,36 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C875" t="n">
+        <v>22</v>
+      </c>
+      <c r="D875" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B875" t="inlineStr">
+      <c r="B876" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C875" t="n">
-        <v>22</v>
-      </c>
-      <c r="D875" t="n">
+      <c r="C876" t="n">
+        <v>22</v>
+      </c>
+      <c r="D876" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D876"/>
+  <dimension ref="A1:D877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16095,16 +16095,16 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/14</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C871" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D871" t="n">
         <v>101</v>
@@ -16113,12 +16113,12 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -16131,12 +16131,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -16149,12 +16149,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -16167,12 +16167,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -16185,18 +16185,36 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C876" t="n">
+        <v>22</v>
+      </c>
+      <c r="D876" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B876" t="inlineStr">
+      <c r="B877" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C876" t="n">
-        <v>22</v>
-      </c>
-      <c r="D876" t="n">
+      <c r="C877" t="n">
+        <v>22</v>
+      </c>
+      <c r="D877" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D877"/>
+  <dimension ref="A1:D878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16113,16 +16113,16 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/15</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C872" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D872" t="n">
         <v>101</v>
@@ -16131,12 +16131,12 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -16149,12 +16149,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -16167,12 +16167,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -16185,12 +16185,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -16203,18 +16203,36 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C877" t="n">
+        <v>22</v>
+      </c>
+      <c r="D877" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B877" t="inlineStr">
+      <c r="B878" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C877" t="n">
-        <v>22</v>
-      </c>
-      <c r="D877" t="n">
+      <c r="C878" t="n">
+        <v>22</v>
+      </c>
+      <c r="D878" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D878"/>
+  <dimension ref="A1:D879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16131,16 +16131,16 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/16</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C873" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D873" t="n">
         <v>101</v>
@@ -16149,12 +16149,12 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -16167,12 +16167,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -16185,12 +16185,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -16203,12 +16203,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -16221,18 +16221,36 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C878" t="n">
+        <v>22</v>
+      </c>
+      <c r="D878" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B878" t="inlineStr">
+      <c r="B879" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C878" t="n">
-        <v>22</v>
-      </c>
-      <c r="D878" t="n">
+      <c r="C879" t="n">
+        <v>22</v>
+      </c>
+      <c r="D879" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D879"/>
+  <dimension ref="A1:D880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16149,16 +16149,16 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/17</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C874" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D874" t="n">
         <v>101</v>
@@ -16167,12 +16167,12 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C875" t="n">
@@ -16185,12 +16185,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -16203,12 +16203,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -16221,12 +16221,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -16239,18 +16239,36 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C879" t="n">
+        <v>22</v>
+      </c>
+      <c r="D879" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B879" t="inlineStr">
+      <c r="B880" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C879" t="n">
-        <v>22</v>
-      </c>
-      <c r="D879" t="n">
+      <c r="C880" t="n">
+        <v>22</v>
+      </c>
+      <c r="D880" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D880"/>
+  <dimension ref="A1:D881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16167,16 +16167,16 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/18</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C875" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D875" t="n">
         <v>101</v>
@@ -16185,12 +16185,12 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C876" t="n">
@@ -16203,12 +16203,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -16221,12 +16221,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -16239,12 +16239,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -16257,18 +16257,36 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C880" t="n">
+        <v>22</v>
+      </c>
+      <c r="D880" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B880" t="inlineStr">
+      <c r="B881" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C880" t="n">
-        <v>22</v>
-      </c>
-      <c r="D880" t="n">
+      <c r="C881" t="n">
+        <v>22</v>
+      </c>
+      <c r="D881" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D881"/>
+  <dimension ref="A1:D882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16185,16 +16185,16 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/19</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C876" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D876" t="n">
         <v>101</v>
@@ -16203,12 +16203,12 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C877" t="n">
@@ -16221,12 +16221,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -16239,12 +16239,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -16257,12 +16257,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -16275,18 +16275,36 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C881" t="n">
+        <v>22</v>
+      </c>
+      <c r="D881" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B881" t="inlineStr">
+      <c r="B882" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C881" t="n">
-        <v>22</v>
-      </c>
-      <c r="D881" t="n">
+      <c r="C882" t="n">
+        <v>22</v>
+      </c>
+      <c r="D882" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D882"/>
+  <dimension ref="A1:D883"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16203,7 +16203,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/20</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -16212,7 +16212,7 @@
         </is>
       </c>
       <c r="C877" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D877" t="n">
         <v>101</v>
@@ -16221,12 +16221,12 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -16239,12 +16239,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -16257,12 +16257,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -16275,12 +16275,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -16293,18 +16293,36 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C882" t="n">
+        <v>22</v>
+      </c>
+      <c r="D882" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B882" t="inlineStr">
+      <c r="B883" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C882" t="n">
-        <v>22</v>
-      </c>
-      <c r="D882" t="n">
+      <c r="C883" t="n">
+        <v>22</v>
+      </c>
+      <c r="D883" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D883"/>
+  <dimension ref="A1:D884"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16221,16 +16221,16 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/21</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C878" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D878" t="n">
         <v>101</v>
@@ -16239,12 +16239,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C879" t="n">
@@ -16257,12 +16257,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -16275,12 +16275,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -16293,12 +16293,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -16311,18 +16311,36 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C883" t="n">
+        <v>22</v>
+      </c>
+      <c r="D883" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B883" t="inlineStr">
+      <c r="B884" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C883" t="n">
-        <v>22</v>
-      </c>
-      <c r="D883" t="n">
+      <c r="C884" t="n">
+        <v>22</v>
+      </c>
+      <c r="D884" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D884"/>
+  <dimension ref="A1:D885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16239,16 +16239,16 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/22</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D879" t="n">
         <v>101</v>
@@ -16257,12 +16257,12 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -16275,12 +16275,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -16293,12 +16293,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -16311,12 +16311,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -16329,18 +16329,36 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C884" t="n">
+        <v>22</v>
+      </c>
+      <c r="D884" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B884" t="inlineStr">
+      <c r="B885" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C884" t="n">
-        <v>22</v>
-      </c>
-      <c r="D884" t="n">
+      <c r="C885" t="n">
+        <v>22</v>
+      </c>
+      <c r="D885" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D885"/>
+  <dimension ref="A1:D886"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16257,16 +16257,16 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/23</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C880" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D880" t="n">
         <v>101</v>
@@ -16275,12 +16275,12 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -16293,12 +16293,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -16311,12 +16311,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -16329,12 +16329,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -16347,18 +16347,36 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C885" t="n">
+        <v>22</v>
+      </c>
+      <c r="D885" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B885" t="inlineStr">
+      <c r="B886" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C885" t="n">
-        <v>22</v>
-      </c>
-      <c r="D885" t="n">
+      <c r="C886" t="n">
+        <v>22</v>
+      </c>
+      <c r="D886" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D886"/>
+  <dimension ref="A1:D887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16275,16 +16275,16 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/24</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>土</t>
         </is>
       </c>
       <c r="C881" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D881" t="n">
         <v>101</v>
@@ -16293,12 +16293,12 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -16311,12 +16311,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -16329,12 +16329,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -16347,12 +16347,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -16365,18 +16365,36 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C886" t="n">
+        <v>22</v>
+      </c>
+      <c r="D886" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B886" t="inlineStr">
+      <c r="B887" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C886" t="n">
-        <v>22</v>
-      </c>
-      <c r="D886" t="n">
+      <c r="C887" t="n">
+        <v>22</v>
+      </c>
+      <c r="D887" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D887"/>
+  <dimension ref="A1:D888"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16293,16 +16293,16 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/25</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>日</t>
         </is>
       </c>
       <c r="C882" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D882" t="n">
         <v>101</v>
@@ -16311,12 +16311,12 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -16329,12 +16329,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -16347,12 +16347,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -16365,12 +16365,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -16383,18 +16383,36 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C887" t="n">
+        <v>22</v>
+      </c>
+      <c r="D887" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B887" t="inlineStr">
+      <c r="B888" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C887" t="n">
-        <v>22</v>
-      </c>
-      <c r="D887" t="n">
+      <c r="C888" t="n">
+        <v>22</v>
+      </c>
+      <c r="D888" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D888"/>
+  <dimension ref="A1:D889"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16311,16 +16311,16 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/26</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>月</t>
         </is>
       </c>
       <c r="C883" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D883" t="n">
         <v>101</v>
@@ -16329,12 +16329,12 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C884" t="n">
@@ -16347,12 +16347,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -16365,12 +16365,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -16383,12 +16383,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -16401,18 +16401,36 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C888" t="n">
+        <v>22</v>
+      </c>
+      <c r="D888" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B888" t="inlineStr">
+      <c r="B889" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C888" t="n">
-        <v>22</v>
-      </c>
-      <c r="D888" t="n">
+      <c r="C889" t="n">
+        <v>22</v>
+      </c>
+      <c r="D889" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D889"/>
+  <dimension ref="A1:D890"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16329,7 +16329,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/27</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="C884" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D884" t="n">
         <v>101</v>
@@ -16347,12 +16347,12 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -16365,12 +16365,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -16383,12 +16383,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -16401,12 +16401,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -16419,18 +16419,36 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C889" t="n">
+        <v>22</v>
+      </c>
+      <c r="D889" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B889" t="inlineStr">
+      <c r="B890" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C889" t="n">
-        <v>22</v>
-      </c>
-      <c r="D889" t="n">
+      <c r="C890" t="n">
+        <v>22</v>
+      </c>
+      <c r="D890" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D890"/>
+  <dimension ref="A1:D891"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16347,16 +16347,16 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/28</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C885" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D885" t="n">
         <v>101</v>
@@ -16365,12 +16365,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -16383,12 +16383,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -16401,12 +16401,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -16419,12 +16419,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -16437,18 +16437,36 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C890" t="n">
+        <v>22</v>
+      </c>
+      <c r="D890" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B890" t="inlineStr">
+      <c r="B891" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C890" t="n">
-        <v>22</v>
-      </c>
-      <c r="D890" t="n">
+      <c r="C891" t="n">
+        <v>22</v>
+      </c>
+      <c r="D891" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D891"/>
+  <dimension ref="A1:D892"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16365,16 +16365,16 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/29</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D886" t="n">
         <v>101</v>
@@ -16383,12 +16383,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -16401,12 +16401,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -16419,12 +16419,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -16437,12 +16437,12 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -16455,18 +16455,36 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C891" t="n">
+        <v>22</v>
+      </c>
+      <c r="D891" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B891" t="inlineStr">
+      <c r="B892" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C891" t="n">
-        <v>22</v>
-      </c>
-      <c r="D891" t="n">
+      <c r="C892" t="n">
+        <v>22</v>
+      </c>
+      <c r="D892" t="n">
         <v>101</v>
       </c>
     </row>

--- a/excel/spotify.xlsx
+++ b/excel/spotify.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D892"/>
+  <dimension ref="A1:D893"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16383,16 +16383,16 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>2026/12/29</t>
+          <t>2026/10/30</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>火</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C887" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D887" t="n">
         <v>101</v>
@@ -16401,12 +16401,12 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2026/12/30</t>
+          <t>2026/12/29</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>火</t>
         </is>
       </c>
       <c r="C888" t="n">
@@ -16419,12 +16419,12 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2026/12/31</t>
+          <t>2026/12/30</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>木</t>
+          <t>水</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -16437,12 +16437,12 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>2027/01/01</t>
+          <t>2026/12/31</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>金</t>
+          <t>木</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -16455,12 +16455,12 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>2027/01/02</t>
+          <t>2027/01/01</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>土</t>
+          <t>金</t>
         </is>
       </c>
       <c r="C891" t="n">
@@ -16473,18 +16473,36 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
+          <t>2027/01/02</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C892" t="n">
+        <v>22</v>
+      </c>
+      <c r="D892" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
           <t>2027/01/03</t>
         </is>
       </c>
-      <c r="B892" t="inlineStr">
+      <c r="B893" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="C892" t="n">
-        <v>22</v>
-      </c>
-      <c r="D892" t="n">
+      <c r="C893" t="n">
+        <v>22</v>
+      </c>
+      <c r="D893" t="n">
         <v>101</v>
       </c>
     </row>
